--- a/pdf2img/tabel/table_1.xlsx
+++ b/pdf2img/tabel/table_1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,18 +453,44 @@
       <c r="L1" t="n">
         <v>11</v>
       </c>
+      <c r="M1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O1" t="n">
+        <v>14</v>
+      </c>
+      <c r="P1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>16</v>
+      </c>
+      <c r="R1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T1" t="n">
+        <v>19</v>
+      </c>
+      <c r="U1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V1" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PEMEGANG:</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SAHAM</t>
-        </is>
-      </c>
+          <t>PEMEGANG,SAHAM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -475,6 +501,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -489,101 +525,239 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bukan</t>
+          <t>Pengendali</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PSP</t>
+          <t>(PSP}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>melalui</t>
+          <t>:</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pasar</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Modal</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(&gt;</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5%)</t>
-        </is>
-      </c>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>Pemegang</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Saham</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bukan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PSP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>melalui</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pasar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Modal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5%)</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pemegang</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>ﬂg{:liﬁ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pengendali</t>
+          <t>;</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(PSP)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>shareholder</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>:Bato'</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sri.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Prof.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>DR.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tahir,</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Dato'</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sri.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Prof.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>DR.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Tahir,</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>¢</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>19,34%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tahir</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>589%</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -591,374 +765,212 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dato’</t>
+          <t>32323232</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sri.</t>
+          <t>;</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prof.</t>
+          <t>annia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DR.</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tahir,</t>
+          <t>12,</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>o</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Gatsu</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Griya</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Megatama,</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JPMCB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Na</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Re-Cathay</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ltd.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>'</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eae</t>
+          <t>o</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>5.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shareholder</t>
+          <t>Masyarakat</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bato'</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tan</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Sri.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Prof.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>DR.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Tahir,</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>MBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jonathan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Tahir</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>589%</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>;</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>875%</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Gatsu</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Griya</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Megatama,</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PT</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ia</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Mevebeda</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Kosi?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>tpatee</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>4,</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JPMCB</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Na</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Re-Cathay</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Lid.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>_8,58%</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5,</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Masyarakat</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>&gt;</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
           <t>20,97%</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
